--- a/r5-aist-trustworthyai-main/ValueSet-eu-case-specific-indication-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-eu-case-specific-indication-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Clinical and administrative reasons for AI application.</t>
+    <t>Clinical and administrative reasons for applying an AI system in a specific case (USE-04).</t>
   </si>
   <si>
     <t>Purpose</t>
